--- a/schoolDocs/StudentImportData/Class6_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class6_ImportReady.xlsx
@@ -724,27 +724,27 @@
   <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="37.705" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="104.832" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="23.423" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="37.705" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="104.832" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -831,6 +831,8 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2">
         <v>16200</v>
       </c>
@@ -869,6 +871,11 @@
       <c r="H3" t="s">
         <v>31</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3">
+        <v>0</v>
+      </c>
       <c r="L3" t="s">
         <v>32</v>
       </c>
@@ -910,8 +917,10 @@
       <c r="H4" t="s">
         <v>39</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4" s="5">
-        <v>8000</v>
+        <v>16200</v>
       </c>
       <c r="L4" t="s">
         <v>40</v>
@@ -954,6 +963,11 @@
       <c r="H5" t="s">
         <v>39</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5">
+        <v>16200</v>
+      </c>
       <c r="L5" t="s">
         <v>46</v>
       </c>
@@ -992,6 +1006,11 @@
       <c r="H6" t="s">
         <v>31</v>
       </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6">
+        <v>0</v>
+      </c>
       <c r="L6" t="s">
         <v>52</v>
       </c>
@@ -1033,6 +1052,8 @@
       <c r="H7" t="s">
         <v>39</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7">
         <v>16200</v>
       </c>
@@ -1071,6 +1092,11 @@
       <c r="H8" t="s">
         <v>31</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8">
+        <v>0</v>
+      </c>
       <c r="L8" t="s">
         <v>62</v>
       </c>
@@ -1112,6 +1138,11 @@
       <c r="H9" t="s">
         <v>31</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9">
+        <v>0</v>
+      </c>
       <c r="L9" t="s">
         <v>67</v>
       </c>
@@ -1147,8 +1178,10 @@
       <c r="H10" t="s">
         <v>39</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
       <c r="K10">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="L10" t="s">
         <v>69</v>
@@ -1182,6 +1215,11 @@
       <c r="H11" t="s">
         <v>31</v>
       </c>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11">
+        <v>0</v>
+      </c>
       <c r="L11" t="s">
         <v>73</v>
       </c>
@@ -1211,6 +1249,11 @@
       <c r="H12" t="s">
         <v>39</v>
       </c>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12">
+        <v>12200</v>
+      </c>
       <c r="L12" t="s">
         <v>77</v>
       </c>
@@ -1249,6 +1292,8 @@
       <c r="H13" t="s">
         <v>39</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
       <c r="K13">
         <v>12200</v>
       </c>
@@ -1290,6 +1335,11 @@
       <c r="H14" t="s">
         <v>31</v>
       </c>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14">
+        <v>0</v>
+      </c>
       <c r="L14" t="s">
         <v>85</v>
       </c>
@@ -1334,6 +1384,7 @@
       <c r="I15">
         <v>25</v>
       </c>
+      <c r="J15"/>
       <c r="K15">
         <v>9150</v>
       </c>
@@ -1378,6 +1429,11 @@
       <c r="H16" t="s">
         <v>31</v>
       </c>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16">
+        <v>0</v>
+      </c>
       <c r="L16" t="s">
         <v>92</v>
       </c>
@@ -1416,6 +1472,11 @@
       <c r="H17" t="s">
         <v>39</v>
       </c>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17">
+        <v>12200</v>
+      </c>
       <c r="L17" t="s">
         <v>97</v>
       </c>
@@ -1454,11 +1515,12 @@
       <c r="H18" t="s">
         <v>87</v>
       </c>
+      <c r="I18"/>
       <c r="J18">
         <v>11000</v>
       </c>
       <c r="K18">
-        <v>11000</v>
+        <v>11000.0</v>
       </c>
       <c r="L18" t="s">
         <v>101</v>

--- a/schoolDocs/StudentImportData/Class6_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class6_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="102">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Aniket Mane</t>
@@ -104,9 +130,6 @@
     <t>19km</t>
   </si>
   <si>
-    <t>CoC student — full ₹16200 collected. Contact in DGA was 9 digits (invalid) — left blank.</t>
-  </si>
-  <si>
     <t>Aradhya Athavale</t>
   </si>
   <si>
@@ -128,7 +151,7 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000039</t>
   </si>
   <si>
     <t>Jayaskumar Bhagat</t>
@@ -149,9 +172,6 @@
     <t>Worker</t>
   </si>
   <si>
-    <t>Partial — ₹8000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Omraj Memane</t>
   </si>
   <si>
@@ -167,9 +187,6 @@
     <t>Works as a helper in a hospital</t>
   </si>
   <si>
-    <t>Single mother family</t>
-  </si>
-  <si>
     <t>Sarthak Tambe</t>
   </si>
   <si>
@@ -185,6 +202,9 @@
     <t>Own farm</t>
   </si>
   <si>
+    <t>25MS000040</t>
+  </si>
+  <si>
     <t>Swaraj Rakshe</t>
   </si>
   <si>
@@ -212,7 +232,7 @@
     <t>Labour</t>
   </si>
   <si>
-    <t>RTE. Contact in DGA was 11 digits (invalid) — left blank.</t>
+    <t>25MS000041</t>
   </si>
   <si>
     <t>Asad Sayyad</t>
@@ -221,6 +241,9 @@
     <t>28/01/2018</t>
   </si>
   <si>
+    <t>25MS000042</t>
+  </si>
+  <si>
     <t>Pavan Pisse</t>
   </si>
   <si>
@@ -230,16 +253,13 @@
     <t>1.5km</t>
   </si>
   <si>
-    <t>Partial — ₹6000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Chanrakant</t>
   </si>
   <si>
     <t>30/01/2018</t>
   </si>
   <si>
-    <t>Only first name — no surname. Assumed male, Class 6. Please verify.</t>
+    <t>25MS000043</t>
   </si>
   <si>
     <t>Anjali Suryawanshi</t>
@@ -275,6 +295,9 @@
     <t>12/01/2020</t>
   </si>
   <si>
+    <t>25MS000044</t>
+  </si>
+  <si>
     <t>Shagufa Ansari</t>
   </si>
   <si>
@@ -287,9 +310,6 @@
     <t>Works at Bekery Shop</t>
   </si>
   <si>
-    <t>DGA total ₹9150 but G col blank — assumed 25% discount. Full amount paid. Please verify.</t>
-  </si>
-  <si>
     <t>Pragati Raut</t>
   </si>
   <si>
@@ -305,6 +325,9 @@
     <t>Business</t>
   </si>
   <si>
+    <t>25MS000045</t>
+  </si>
+  <si>
     <t>Vaishali Kokare</t>
   </si>
   <si>
@@ -324,9 +347,6 @@
   </si>
   <si>
     <t>Bhandgaon</t>
-  </si>
-  <si>
-    <t>No standard fee % in DGA — ₹11000 used as custom fee. Please verify.</t>
   </si>
 </sst>
 </file>
@@ -378,12 +398,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -391,6 +405,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -412,16 +432,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,7 +764,7 @@
     <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="104.832" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -778,10 +798,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -808,7 +828,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -845,16 +865,14 @@
       <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -869,7 +887,7 @@
         <v>7262882149</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
@@ -877,22 +895,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>34</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>35</v>
       </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
         <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -900,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -915,38 +933,36 @@
         <v>7498538896</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>16200</v>
       </c>
       <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
         <v>40</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>41</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>42</v>
       </c>
-      <c r="P4" t="s">
-        <v>43</v>
-      </c>
       <c r="R4" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" t="s">
-        <v>44</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -961,7 +977,7 @@
         <v>7028882067</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -969,27 +985,25 @@
         <v>16200</v>
       </c>
       <c r="L5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s">
         <v>46</v>
       </c>
-      <c r="M5" t="s">
+      <c r="P5" t="s">
         <v>47</v>
       </c>
-      <c r="N5" t="s">
-        <v>48</v>
-      </c>
-      <c r="P5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" t="s">
-        <v>50</v>
-      </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1004,7 +1018,7 @@
         <v>7841035181</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -1012,22 +1026,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" t="s">
         <v>52</v>
       </c>
-      <c r="M6" t="s">
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="U6" t="s">
         <v>53</v>
-      </c>
-      <c r="N6" t="s">
-        <v>54</v>
-      </c>
-      <c r="P6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -1035,7 +1049,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1050,7 +1064,7 @@
         <v>9623158476</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1058,27 +1072,28 @@
         <v>16200</v>
       </c>
       <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s">
         <v>57</v>
       </c>
-      <c r="M7" t="s">
+      <c r="P7" t="s">
         <v>58</v>
       </c>
-      <c r="N7" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" t="s">
-        <v>60</v>
-      </c>
       <c r="R7" t="s">
-        <v>36</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -1090,7 +1105,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1098,22 +1113,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" t="s">
         <v>62</v>
       </c>
-      <c r="M8" t="s">
+      <c r="R8" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" t="s">
         <v>63</v>
-      </c>
-      <c r="N8" t="s">
-        <v>34</v>
-      </c>
-      <c r="P8" t="s">
-        <v>64</v>
-      </c>
-      <c r="R8" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1121,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1136,7 +1151,7 @@
         <v>7822936079</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1144,16 +1159,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M9" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" t="s">
         <v>41</v>
       </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
       <c r="U9" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1161,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1176,7 +1191,7 @@
         <v>9322820183</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1184,24 +1199,22 @@
         <v>10000</v>
       </c>
       <c r="L10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" t="s">
         <v>69</v>
       </c>
-      <c r="M10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" t="s">
-        <v>70</v>
-      </c>
-      <c r="U10" t="s">
-        <v>71</v>
-      </c>
+      <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -1213,7 +1226,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1221,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1232,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -1247,7 +1260,7 @@
         <v>7057125914</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1255,30 +1268,31 @@
         <v>12200</v>
       </c>
       <c r="L12" t="s">
+        <v>75</v>
+      </c>
+      <c r="M12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N12" t="s">
+        <v>57</v>
+      </c>
+      <c r="P12" t="s">
+        <v>62</v>
+      </c>
+      <c r="R12" t="s">
         <v>77</v>
       </c>
-      <c r="M12" t="s">
-        <v>78</v>
-      </c>
-      <c r="N12" t="s">
-        <v>59</v>
-      </c>
-      <c r="P12" t="s">
-        <v>64</v>
-      </c>
-      <c r="R12" t="s">
-        <v>79</v>
-      </c>
+      <c r="U12"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1290,7 +1304,7 @@
         <v>9763193486</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1298,30 +1312,31 @@
         <v>12200</v>
       </c>
       <c r="L13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M13" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" t="s">
+        <v>80</v>
+      </c>
+      <c r="R13" t="s">
         <v>81</v>
       </c>
-      <c r="N13" t="s">
-        <v>48</v>
-      </c>
-      <c r="P13" t="s">
-        <v>82</v>
-      </c>
-      <c r="R13" t="s">
-        <v>83</v>
-      </c>
+      <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1333,7 +1348,7 @@
         <v>9049764023</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1341,22 +1356,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M14" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" t="s">
         <v>33</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" t="s">
         <v>34</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>35</v>
       </c>
-      <c r="R14" t="s">
-        <v>36</v>
-      </c>
       <c r="U14" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1364,10 +1379,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1379,7 +1394,7 @@
         <v>6395064076</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I15">
         <v>25</v>
@@ -1389,33 +1404,31 @@
         <v>9150</v>
       </c>
       <c r="L15" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+      <c r="P15" t="s">
         <v>88</v>
       </c>
-      <c r="M15" t="s">
-        <v>63</v>
-      </c>
-      <c r="N15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" t="s">
-        <v>89</v>
-      </c>
       <c r="R15" t="s">
-        <v>36</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>90</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1427,7 +1440,7 @@
         <v>9960501315</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1435,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" t="s">
+        <v>91</v>
+      </c>
+      <c r="N16" t="s">
         <v>92</v>
       </c>
-      <c r="M16" t="s">
+      <c r="P16" t="s">
         <v>93</v>
       </c>
-      <c r="N16" t="s">
+      <c r="U16" t="s">
         <v>94</v>
-      </c>
-      <c r="P16" t="s">
-        <v>95</v>
-      </c>
-      <c r="U16" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1455,10 +1468,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1470,7 +1483,7 @@
         <v>9975332700</v>
       </c>
       <c r="H17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -1478,30 +1491,31 @@
         <v>12200</v>
       </c>
       <c r="L17" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" t="s">
         <v>97</v>
       </c>
-      <c r="M17" t="s">
-        <v>63</v>
-      </c>
-      <c r="N17" t="s">
+      <c r="P17" t="s">
         <v>98</v>
       </c>
-      <c r="P17" t="s">
-        <v>99</v>
-      </c>
       <c r="R17" t="s">
-        <v>36</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="U17"/>
     </row>
     <row r="18" spans="1:21">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1513,7 +1527,7 @@
         <v>9096462142</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I18"/>
       <c r="J18">
@@ -1523,17 +1537,15 @@
         <v>11000.0</v>
       </c>
       <c r="L18" t="s">
+        <v>100</v>
+      </c>
+      <c r="M18" t="s">
         <v>101</v>
       </c>
-      <c r="M18" t="s">
-        <v>102</v>
-      </c>
       <c r="N18" t="s">
-        <v>59</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>103</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="U18" s="4"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -1547,6 +1559,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class6_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class6_ImportReady.xlsx
@@ -865,6 +865,9 @@
       <c r="N2" t="s">
         <v>28</v>
       </c>
+      <c r="S2">
+        <v>27000010113</v>
+      </c>
       <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
@@ -909,6 +912,9 @@
       <c r="R3" t="s">
         <v>35</v>
       </c>
+      <c r="S3">
+        <v>27000010114</v>
+      </c>
       <c r="U3" t="s">
         <v>36</v>
       </c>
@@ -955,6 +961,9 @@
       <c r="R4" t="s">
         <v>35</v>
       </c>
+      <c r="S4">
+        <v>27000010115</v>
+      </c>
       <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
@@ -996,6 +1005,9 @@
       <c r="P5" t="s">
         <v>47</v>
       </c>
+      <c r="S5">
+        <v>27000010116</v>
+      </c>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
@@ -1040,6 +1052,9 @@
       <c r="R6" t="s">
         <v>35</v>
       </c>
+      <c r="S6">
+        <v>27000010117</v>
+      </c>
       <c r="U6" t="s">
         <v>53</v>
       </c>
@@ -1086,6 +1101,9 @@
       <c r="R7" t="s">
         <v>35</v>
       </c>
+      <c r="S7">
+        <v>27000010118</v>
+      </c>
       <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
@@ -1127,6 +1145,9 @@
       <c r="R8" t="s">
         <v>62</v>
       </c>
+      <c r="S8">
+        <v>27000010119</v>
+      </c>
       <c r="U8" t="s">
         <v>63</v>
       </c>
@@ -1167,6 +1188,9 @@
       <c r="N9" t="s">
         <v>41</v>
       </c>
+      <c r="S9">
+        <v>27000010120</v>
+      </c>
       <c r="U9" t="s">
         <v>66</v>
       </c>
@@ -1207,6 +1231,9 @@
       <c r="N10" t="s">
         <v>69</v>
       </c>
+      <c r="S10">
+        <v>27000010121</v>
+      </c>
       <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
@@ -1236,6 +1263,9 @@
       <c r="L11" t="s">
         <v>71</v>
       </c>
+      <c r="S11">
+        <v>27000010122</v>
+      </c>
       <c r="U11" s="4" t="s">
         <v>72</v>
       </c>
@@ -1282,6 +1312,9 @@
       <c r="R12" t="s">
         <v>77</v>
       </c>
+      <c r="S12">
+        <v>27000010123</v>
+      </c>
       <c r="U12"/>
     </row>
     <row r="13" spans="1:21">
@@ -1326,6 +1359,9 @@
       <c r="R13" t="s">
         <v>81</v>
       </c>
+      <c r="S13">
+        <v>27000010124</v>
+      </c>
       <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
@@ -1370,6 +1406,9 @@
       <c r="R14" t="s">
         <v>35</v>
       </c>
+      <c r="S14">
+        <v>27000010125</v>
+      </c>
       <c r="U14" t="s">
         <v>84</v>
       </c>
@@ -1417,6 +1456,9 @@
       </c>
       <c r="R15" t="s">
         <v>35</v>
+      </c>
+      <c r="S15">
+        <v>27000010126</v>
       </c>
       <c r="U15" s="4"/>
     </row>
@@ -1459,6 +1501,9 @@
       <c r="P16" t="s">
         <v>93</v>
       </c>
+      <c r="S16">
+        <v>27000010127</v>
+      </c>
       <c r="U16" t="s">
         <v>94</v>
       </c>
@@ -1505,6 +1550,9 @@
       <c r="R17" t="s">
         <v>35</v>
       </c>
+      <c r="S17">
+        <v>27000010128</v>
+      </c>
       <c r="U17"/>
     </row>
     <row r="18" spans="1:21">
@@ -1544,6 +1592,9 @@
       </c>
       <c r="N18" t="s">
         <v>57</v>
+      </c>
+      <c r="S18">
+        <v>27000010129</v>
       </c>
       <c r="U18" s="4"/>
     </row>
